--- a/测试_补全结果.xlsx
+++ b/测试_补全结果.xlsx
@@ -499,16 +499,9 @@
           <t>兰卡椰壳</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>兰卡</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>兰卡椰壳是一种优质的园艺栽培介质，采用天然椰壳为原料，经过处理加工而成。具有良好的透气性和排水性，能有效改善土壤结构，防止土壤板结。适用于兰花种植、多肉植物栽培以及各类花卉的土壤改良。可作为栽培基质直接使用，也可混合其他介质调节土壤通透性。天然环保，无病虫害，是家庭园艺和专业种植的理想选择。</t>
+          <t>兰卡椰壳是一种优质的土壤改良材料，采用进口椰壳原料经过加工处理而成。具有良好的透气性、排水性和保水性，能有效改善土壤结构，增加土壤松软度。其天然有机特性适合用于兰科植物、多肉植物、盆栽花卉等养护，可作为栽培基质的主要成分或与其他介质混合使用。是家庭园艺和专业种植中常用的介质改良材料，安全环保，适合长期使用。</t>
         </is>
       </c>
     </row>
@@ -548,11 +541,9 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>帝罗马国际盆白陶系列，选用优质白色陶瓷材质，质感细腻温润，外观简约大方。陶瓷盆具有良好的透气性和排水性，能为植物根系提供健康的生长环境。适合用于室内外绿植、花卉的栽培与摆设，是家庭园艺和商业景观的理想选择。盆体坚固耐用，便于清洁和重复使用。</t>
+          <t>帝罗马国际盆白陶15是一款高品质陶瓷花盆，采用白色陶瓷材质，设计简约大方，质感细腻。该盆具有良好的透气性和排水性，适合种植各类室内外植物。陶瓷材质坚固耐用，抗老化性强，适合长期使用。规格15寸，适宜种植中大型植物，如绿植、开花植物或多肉植物等。</t>
         </is>
       </c>
     </row>
@@ -587,12 +578,9 @@
           <t>椰糠</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>印度椰糠低盐版是优质的园艺栽培介质，由椰子外壳纤维加工而成。其低盐配方适合对盐分敏感的植物使用，保水性和透气性优异，可改良土壤结构。适用于多肉植物、花卉、蔬菜等多种园艺场景，可单独使用或与其他介质混合使用，是家庭园艺和商业种植的理想选择。</t>
+          <t>印度椰糠是一种优质的园艺栽培介质，由椰子外壳加工而成。经过低盐处理，EC值低，适合对盐分敏感的植物使用。椰糠具有良好的透气性、保水性和排水性，质地轻盈，pH值呈弱酸性至中性，富含植物生长所需的有机质。可单独使用或与泥炭土、珍珠岩等混合配制成通用栽培介质，适用于多肉植物、花卉、蔬菜育苗及盆栽栽培。低盐印度椰糠是家庭园艺和商业花卉生产中常用的优质介质材料。</t>
         </is>
       </c>
     </row>
@@ -619,24 +607,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>特肥</t>
+          <t>通用肥</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>其他特肥</t>
+          <t>其他通用肥</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>福袋花彩师</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>花彩师</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>福袋花彩师植物营养颗粒（爆花型）是一款专为促进花卉开花设计的园艺肥料产品，规格为16g。该产品采用颗粒状配方，便于均匀撒施或穴施，能够为开花植物提供充足的磷钾营养，有效促进花芽分化、增加花苞数量、提升开花质量。适用于月季、绣球、茉莉、三角梅等各类开花植物的追肥使用。使用时可根据植物大小和生长阶段适量施用，配合浇水效果更佳，注意避免直接接触叶片以防灼伤。</t>
+          <t>花彩师爆花型植物营养颗粒是一款专为促进开花设计的园艺肥料，小包装16g方便家庭使用。颗粒状肥料易于均匀撒施，可直接撒于盆土表面或浅埋土中。建议在花期前和花期中使用，帮助植物补充开花所需营养，促进花芽分化，增加开花数量和花色鲜艳度。适用于各类开花植物，如月季、绣球、铁线莲等观赏花卉。使用时注意控制用量，避免过量造成肥害。</t>
         </is>
       </c>
     </row>
@@ -676,11 +662,9 @@
           <t>园艺家</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>成都神龙代工生产的园艺家品牌花盆，12升容量，适合种植中大型花卉、蔬菜或小型灌木。采用优质塑料材质，轻便耐用，排水透气性好，便于家庭园艺种植使用。</t>
+          <t>成都神龙代工生产的园艺家品牌塑料盆，容量为12升，适合家庭园艺种植使用。采用优质塑料材质，轻便耐用，底部设有排水孔设计，可有效防止积水烂根。12L容量适合种植中小型花卉、蔬菜或小型灌木，是阳台园艺和室内绿化的实用容器选择。</t>
         </is>
       </c>
     </row>
@@ -715,12 +699,14 @@
           <t>椰糠</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>印度椰糠颗粒是一种优质的有机栽培介质，由椰子外壳加工而成。具有良好的透气性、保水性和排水性，pH值呈弱酸性至中性，适合大多数园艺植物种植。可单独使用或与其他介质混合使用，适用于多肉植物、花卉、蔬菜等的栽培。能有效改善土壤结构，促进根系生长发育，是一种环保可持续的园艺材料。</t>
+          <t>印度椰糠颗粒是一种优质的园艺栽培介质，由椰子外壳纤维加工而成。具有良好的透气性、保水性和排水性，pH值呈弱酸性至中性，适合大多数植物生长。可单独使用或与其他介质混合使用，广泛应用于盆栽花卉、蔬菜育苗、扦插繁殖等场景。椰糠颗粒状便于使用，不易结块，能有效改善土壤结构，是现代园艺栽培中常用的环保型介质材料。</t>
         </is>
       </c>
     </row>
@@ -772,7 +758,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>风雨兰“胖丽丽”是一款广受欢迎的宿根球根花卉，属于石蒜科葱莲属。其花型圆润饱满，花瓣粉白相间，清新可爱，具有极高的观赏价值。该品种适应性强，耐热耐寒，易于养护，适合庭院地栽或盆栽观赏。花期集中在夏秋季节，单朵花可维持3-5天左右。喜阳光充足的环境，排水良好的土壤有助于球根健康生长。2年球规格表示球根已生长2年，活力充沛，种植后当年即可开花。</t>
+          <t>风雨兰“胖丽丽”是虹安宿根品牌推出的经典品种，为多年生常绿球根花卉。该品种株型紧凑，叶片细长如韭菜，花朵圆润饱满，呈粉色或白色，娇小可爱。球茎经过2年培育，生命力旺盛，繁殖能力强。适合庭院地栽、花境边缘或盆栽观赏，雨后易开花，花期较长。喜阳光充足、排水良好的环境，耐热耐旱，养护简单，是阳台和花园的理想点缀植物。</t>
         </is>
       </c>
     </row>
@@ -824,7 +810,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>虹安果树蓝莓“蓝葡萄”是一款优质蓝莓品种，种苗苗木类灌木植物。植株生长旺盛，果实呈深蓝色，果粒大而饱满，口感甜脆多汁，香味浓郁。该品种适应性强，耐寒性好，适合庭院种植或规模化栽培。喜酸性土壤（pH值4.5-5.5），需充足阳光和良好排水环境。花期春季，果期夏初，观赏与食用价值兼具。种植时需注意保持土壤酸性，适当施肥，并做好冬季修剪管理。</t>
+          <t>虹安果树蓝莓'蓝葡萄'是一款优质南高丛蓝莓品种，果实大粒、香甜多汁、产量稳定。该品种树势中等，株型紧凑，适合庭院种植或规模化栽培。需注意异花授粉以提高坐果率。喜酸性土壤（pH值4.5-5.5），需充足阳光和良好排水条件。果实成熟期较早，适合家庭园艺爱好者种植品尝新鲜蓝莓。耐寒性较好，适应性广。</t>
         </is>
       </c>
     </row>
@@ -864,11 +850,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>花彩师植物营养液通用型是一款高效水溶肥料，富含氮磷钾及微量元素，适用于各类室内外植物的追肥使用。采用科学配比，溶解迅速，吸收率高，可促进植物生长发育，增强抗病能力。无残留、无污染，使用安全方便。按照说明稀释后浇灌或叶面喷施均可，建议每7-14天使用一次效果更佳。</t>
+          <t>花彩师植物营养液通用型是一种高效水溶性肥料，规格为18g/袋。该产品采用科学配比，富含氮磷钾及微量元素，适用于各类花卉、蔬菜、果树的追肥使用。能快速补充植物生长所需养分，促进植株健壮生长、叶色浓绿、花果丰满。使用时按比例稀释后浇灌或叶面喷施，操作简便，是家庭园艺和农业生产中常用的优质肥料。</t>
         </is>
       </c>
     </row>
@@ -900,7 +884,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>其他通用肥</t>
+          <t>水溶肥</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -908,11 +892,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>花彩师生根液是一种植物生长调节剂，主要成分为吲哚丁酸钾等生根物质，能促进植物根系发育，加速扦插枝条生根，提高移栽成活率。适用于各类花卉、蔬菜、林木的扦插繁殖及移栽促根。使用时需稀释后浇灌或浸泡插条，浓度不宜过高，以免造成药害。应置于阴凉干燥处保存，避免儿童触及。</t>
+          <t>花彩师生根液是一种植物根系促进剂，主要成分通常包含植物生长激素和营养元素，能有效刺激植物根系快速生长发育，提高移栽成活率。适用于扦插繁殖、苗木移栽、种子催芽等场景。使用时需按说明稀释后浇灌或浸泡植株根部，50ml小包装适合家庭园艺少量使用，注意避免浓度过高造成肥害。</t>
         </is>
       </c>
     </row>
@@ -927,14 +909,46 @@
           <t>虹安宿根 紫菀"小卡罗"</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>多年生草本</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>其他多年生草本</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>虹安</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>紫菀</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>小卡罗</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>紫菀'小卡罗'是多年生宿根草本花卉，株高约40-60厘米，秋季开花，花朵呈紫色或蓝紫色，花量大而密集，花期长。性强健，耐寒耐热，对土壤要求不严，适合花境配置、林缘种植或盆栽观赏。喜阳光充足环境，也可耐半阴，花后及时修剪可促进二次开花，是秋季花园重要的蜜源植物和观花品种。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -969,7 +983,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>虹安果树</t>
+          <t>虹安</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -984,7 +998,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>圆叶葡萄红宝石是优良的水果型葡萄品种，原产美国南部，果穗圆锥形，果粒椭圆形，成熟时呈宝石红色，糖度高，口感甜脆。树势旺盛，适应性广，适合庭院种植或规模化栽培。藤本植物，需搭架支撑，喜阳光充足，排水良好的环境。春季开花，夏季结果，果实既可鲜食也可加工。是兼具观赏与食用价值的藤本果树，适合家庭园艺种植。</t>
+          <t>圆叶葡萄“红宝石”是葡萄科葡萄属的优质藤本果树品种，原产北美东部，因叶片圆润而得名。其果实成熟时呈深紫红色，光泽如宝石，故名“红宝石”。果肉紧实，口感甜脆多汁，风味独特。该品种适应性强，抗病性好，产量稳定，适合庭院攀爬架或规模化栽培。喜阳光充足、排水良好的环境，耐热耐寒，栽培难度较低。</t>
         </is>
       </c>
     </row>
@@ -1024,11 +1038,9 @@
           <t>花逸乐</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>花逸乐海藻有机颗粒肥是一款以天然海藻为主要原料的有机肥料产品，颗粒状设计便于均匀撒施。有机成分能改良土壤结构，增加土壤肥力，促进植物根系健康生长。适用于家庭园艺中各类花卉、蔬菜、果树的底肥和追肥使用，安全温和，不易烧根。4kg包装适合中小规模园艺种植需求。</t>
+          <t>花逸乐海藻有机颗粒肥是一种以天然海藻为原料精制而成的有机肥料，富含植物生长所需的氮、磷、钾等大量元素及微量元素、氨基酸和海藻多糖等活性物质。颗粒状设计便于均匀撒施，可改良土壤结构，增加土壤有机质含量，促进土壤微生物活动。适用于各类花卉、蔬菜、果树等植物的基肥和追肥，能有效促进植物根系发育、增强抗病抗逆能力，提高果实品质。安全环保，适合家庭园艺和农业生产使用。</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1092,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>蓝莓"追雪"是小铃铛系列品种，为落叶灌木，株型紧凑适合盆栽。果实呈淡蓝色，果粉充足，风味酸甜可口，品质优良。该品种丰产性强，花期春季，果期夏秋季。喜酸性土壤（pH值4.5-5.5），需充足阳光和良好排水。适合庭院种植或阳台盆栽，需注意人工授粉以提高坐果率。耐寒性较好，北方地区可露地越冬。</t>
+          <t>虹安果树蓝莓品种"追雪"，别名小铃铛，为蓝莓灌木种苗。植株生长旺盛，果实品质优良，适应性较强。适合家庭园艺种植于阳台、庭院，既能观赏又可采收果实。喜酸性疏松土壤，需充足光照，浇水需保持土壤微湿，避免积水。北方地区需注意冬季防寒保护。</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1144,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>虹安铁线莲乌托邦是铁线莲中的一个优秀品种，花朵呈星形，花色通常为淡紫色或蓝紫色，花瓣带有优美的波浪边缘，开花量大，花期较长。适合种植在阳光充足或半阴的环境中，需搭设支架让其攀援生长，可用于阳台花架、庭院围栏、墙面绿化等。该品种抗病性较强，养护相对简单，喜欢排水良好、肥沃的土壤环境。冬季需注意适当修剪枯枝，来年可萌发更多新枝开花。</t>
+          <t>虹安铁线莲乌托邦是一款藤本花卉苗木，植株攀援性强，花朵大而艳丽，花色独特，具有较高的观赏价值。适合用于庭院花架、栅栏、阳台绿化等场景。喜阳光充足、排水良好的环境，耐寒性较好，养护相对简单，是园艺爱好者喜爱的经典品种。</t>
         </is>
       </c>
     </row>
@@ -1172,11 +1184,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>花彩师缓释肥料是一种专业园艺肥料，氮磷钾比例为14-14-14，并添加TE（微量元素），可满足植物全面营养需求。采用缓释技术，肥效持久释放，减少施肥次数，使用方便。适用于各类花卉、蔬菜、果树及观叶植物的基肥或追肥使用。20g小包装设计，适合家庭园艺少量使用或盆栽基肥配制。使用时按说明书比例稀释或混土使用，避免直接接触根系造成肥害。</t>
+          <t>花彩师缓释肥料通用型是一款专为家庭园艺设计的长效缓释肥料，氮磷钾比例为14-14-14，并添加TE微量元素配方，养分均衡全面。采用先进的缓释技术，养分释放缓慢持久，可持续供应植物营养约2-3个月，减少施肥次数。适用于各类室内外观赏植物、蔬菜、果树等的基肥和追肥使用。20g小包装设计，适合阳台园艺、小盆栽使用，方便控制用量，避免浪费。使用时均匀撒施于盆土表面或浅埋土中，浇水后养分析出供根系吸收。注意避光防潮保存，开封后尽快使用以保证肥效。</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1238,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>铁线莲是毛茛科铁线莲属的多年生藤本植物，被誉为“藤本皇后”。倒影是铁线莲的一个优秀品种，花朵呈淡雅色调，攀援能力强，适合用于花架、拱门、墙面等垂直绿化。该品种耐寒性较好，花期集中在春夏季，观赏价值高。喜阳光充足、排水良好的环境，栽培时需注意避免积水，冬季适当修剪枯枝可促进来年开花。</t>
+          <t>虹安铁线莲"倒影"是一款具有独特观赏价值的藤本花卉品种。其花色清新雅致，花型优美，攀援能力强，适合用于花架、廊架、栅栏等垂直绿化装饰。该品种适应性较强，喜阳光充足、排水良好的环境，耐寒性较好，适合庭院种植或盆栽观赏。花期较长，可从春季持续至秋季，是打造浪漫花园氛围的理想选择。</t>
         </is>
       </c>
     </row>
@@ -1273,14 +1283,9 @@
           <t>黑莓</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>组培</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>黑莓是深受消费者喜爱的浆果果树，果实呈黑紫色，口感酸甜，富含花青素等营养成分。组培苗采用植物组织培养技术繁殖，遗传稳定性好，生长健壮，适应性强。适宜在阳光充足、排水良好的环境中种植，喜欢微酸性土壤。果实可鲜食，也可制作成果酱、果汁等加工品。种植后一般2-3年进入盛果期，经济价值较高。</t>
+          <t>黑莓是蔷薇科悬钩子属的灌木植物，果实呈黑色或深紫色，酸甜可口，营养丰富。本品为组培苗，具有繁殖速度快、遗传性状稳定、苗木健壮等优点。黑莓喜温暖湿润环境，耐寒性较强，适合庭院种植或规模化栽培。种植时需选择阳光充足、排水良好的土壤，生长期注意合理修剪和施肥，促进多分枝，提高果实产量。</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1320,14 @@
           <t>其他浇水工具</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>未提供</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>外螺纹内牙管件是一种管道连接配件，30040G为具体型号规格。该产品采用内外螺纹设计，可实现不同管道系统之间的连接和转换。常见材质包括铜、不锈钢、PVC等。具有密封性好、安装方便、耐腐蚀等特点。主要用于灌溉系统、水管连接、园艺设备配套等场景。在园艺应用中常用于组装灌溉管网、连接水泵与出水口等。使用时需注意螺纹规格匹配，并做好密封处理以防漏水。</t>
+          <t>外螺纹内牙转换接头，型号30040G，是一种园艺灌溉系统管道连接配件。产品采用外螺纹与内牙设计，用于连接不同规格的灌溉管道，实现水路的转换与延伸。材质通常为铜或不锈钢，具有耐腐蚀、耐高压特性，适用于花园灌溉、滴灌系统、自动浇水系统等场景的管道布局与改造。使用时需配合密封胶带确保连接处不漏水。</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1379,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>铁线莲是多年生藤本植物，有藤本皇后之美称。乌托邦品种花大色艳，花期较长，适应性较强。虹安是铁线莲专业苗圃品牌，品质有保障。适合庭院、阳台种植，可做花墙、花架、拱门等。喜阳光充足、排水良好的环境，耐寒性较好，冬季地上部分枯萎，地下部分翌年重新萌发。种植时需搭设攀爬架，夏季注意适当遮阴，花后及时修剪。</t>
+          <t>虹安铁线莲乌托邦是虹安品牌旗下的藤本花卉品种，花朵大而艳丽，花色独特，具有较高的观赏价值。该品种适应性强，耐寒性较好，适合庭院种植或阳台盆栽，可用于花架、栅栏、墙面等垂直绿化。喜欢阳光充足但忌强光暴晒，通风良好的环境有利于其健康生长。浇水遵循见干见湿原则，生长期适当施肥可促进开花。</t>
         </is>
       </c>
     </row>
@@ -1412,11 +1419,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>花彩师品牌通用肥料，氮磷钾等营养元素配比均衡，适用于家庭园艺各类植物的日常施肥。可在植物生长季节稀释后浇灌或叶面喷施使用，为植物提供充足的养分支持，促进植株健康生长。具体使用方法及稀释比例请参照产品说明书。</t>
+          <t>花彩师品牌下的园艺肥料产品，1%浓度可能指某种微量元素或营养成分的含量。适用于家庭园艺植物的日常养护，可溶于水后浇灌或叶面喷施，使用方便，具体施肥方法请参照产品说明书。</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1473,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>大花绣球角宿一是绣球花的一个品种，属于灌木类落叶花卉。该品种花球大而饱满，色彩丰富，具有极高的观赏价值。适合庭院种植、阳台盆栽或花境布置。喜半阴环境，不耐强光直射，需保持土壤湿润。冬季落叶后适当修剪残花枯枝，有利于来年开花。花期通常在春末至夏季，是夏季花园的重要观赏花卉之一。</t>
+          <t>大花绣球角宿一是绣球花中的一个优选品种，以其大而丰满的花球著称。花色随土壤酸碱度变化，酸性土壤呈蓝色，碱性土壤呈粉红色，具有极高的观赏价值。适合种植于庭院、花坛或阳台，喜欢半阴环境，需保持土壤湿润但避免积水。绣球花期较长，一般从春末持续到夏初，花朵可作为切花使用，也可干燥后作为永生花装饰。</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1525,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>虹安铁线莲乌托邦是虹安品牌推出的藤本花卉种苗。铁线莲被誉为"藤本皇后"，乌托邦品种花型优美，花色鲜艳，极具观赏价值。该品种适应性强，喜阳光充足、排水良好的环境，适合庭院、阳台种植，可攀援栅栏、花架、拱门等。其花期较长，养护简单，是广受欢迎的藤本花卉品种。</t>
+          <t>铁线莲是毛茛科铁线莲属多年生藤本植物，花色丰富、花型多样，有“藤本皇后”之称。乌托邦是铁线莲中的一个经典品种，花朵大而艳丽，攀援能力强，适合用于花架、拱门、墙面等园林景观的垂直绿化，也可盆栽观赏。喜阳光充足、排水良好的环境，耐寒性较强。</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1562,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>安镇</t>
+          <t>XQZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1572,7 +1577,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>安镇大花绣球"露娜"是绣球花中的经典品种，花朵大而饱满，呈球形花序，具有极高的观赏价值。该品种适应性强，耐阴性好，适合庭院种植或盆栽观赏。花色随土壤酸碱度变化，酸性土壤呈蓝色，碱性土壤呈粉红色。春季开花，花期较长，养护简单，需要保持土壤湿润，避免强光直射。</t>
+          <t>安镇大花绣球露娜是绣球花中的一个优秀品种，花朵大而饱满，花色丰富艳丽，具有极高的观赏价值。该品种适应性强，耐寒性较好，适合庭院种植或盆栽观赏。绣球花喜半阴环境，不耐强光直射，喜欢疏松肥沃、排水良好的土壤。春季萌芽期需保持充足水分，生长期适当施肥，花后及时修剪残花，有利于来年开花。</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1629,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>蓝莓追雪是一款早熟蓝莓品种，果实较大，果肉细腻，甜度高，酸度适中，香气浓郁。该品种适应性强，耐寒性较好，适合我国大部分地区种植。蓝莓喜酸性土壤，喜阳光充足环境，需保持土壤湿润但排水良好。追雪蓝莓产量稳定，是庭院种植和商业栽培的优选品种，既可鲜食也可加工成果酱、果汁等。</t>
+          <t>蓝莓追雪是虹安果树品牌下的蓝莓品种，属于灌木类果树。植株紧凑，适合庭院种植或盆栽。果实呈淡蓝色，果肉细腻，酸甜可口，富含花青素，具有较高的营养价值。喜酸性土壤（pH值4.5-5.5），需充足阳光，适应性较强，耐寒性较好。成熟期较早，丰产性好，是家庭园艺中受欢迎的蓝莓品种之一。</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1656,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>灌木</t>
+          <t>乔木</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>其他灌木</t>
+          <t>其他乔木</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1671,12 +1676,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R香檬</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>虹安R香檬是虹安果树品牌推出的柑橘类种苗苗木。香檬又名台湾香檬、山柑橘，是芸香科柑橘属多年生灌木植物。植株树形紧凑，枝叶茂盛，果实呈扁圆形，成熟时呈金黄色，果皮薄而有香气，果肉酸甜可口。该品种适合庭院种植或盆栽观赏，既可作为观赏植物美化环境，又可收获果实用于食用或加工。喜阳光充足的环境，耐热耐寒，土壤适应性较强，浇水遵循见干见湿原则，生长季节适当施肥促进开花结果。</t>
+          <t>虹安R香檬是台湾香檬（Citrus depressa）的优良品种，又称山柚柑或扁皮柠檬。香檬为柑橘类常绿灌木或小乔木，果实小巧圆润，果皮薄而有香气，果汁丰富酸甜适中，富含维生素C和类黄酮等营养成分。此品种适应性强，耐热耐寒，适合庭院种植或规模化栽培，既可观赏又可采收果实，成熟期集中，便于管理。喜阳光充足、排水良好的环境，需适当修剪以保持良好树形。</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1708,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>特肥</t>
+          <t>通用肥</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>其他特肥</t>
+          <t>水溶肥</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1716,11 +1721,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>花彩师园艺磷酸二氢钾是一种高浓度速效肥料，磷钾含量丰富，不含氮元素。磷酸二氢钾水溶性好，易被植物吸收利用，可促进花芽分化、提高坐果率、增强抗逆性。适用于花卉、果蔬、苗木等各类植物的追肥使用，可叶面喷施或根部浇灌。建议按照说明稀释后使用，避免浓度过高造成肥害。可与多种肥料和农药混用，使用方便。</t>
+          <t>花彩师园艺磷酸二氢钾是一种高浓度速效水溶肥料，磷钾含量高，纯度好，溶解快速，适合叶面喷施或灌根使用。可促进花卉果蔬根系发育、花芽分化、果实膨大，提高植物抗病抗逆能力。适用于开花植物结果期及球根花卉膨大期，使用时需按照推荐浓度稀释，避免浓度过高造成肥害。</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1758,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -1768,7 +1770,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>冬青先令是冬青科冬青属的常绿乔木品种，株型端正，枝叶茂密。叶片深绿色且有光泽，冬季不落叶，具有良好的观赏价值。先令品种生长速度适中，耐修剪，适应性强，适合作为庭院行道树或景观节点的主景树。喜阳光充足的环境，耐寒性较强，对土壤要求不严，但在排水良好的肥沃土壤中生长更佳。冬季观果效果佳，红色的果实簇生于枝头，为萧瑟的冬季增添一抹亮色。</t>
+          <t>冬青“先令”是一款常绿乔木品种，株型紧凑，叶片深绿有光泽，四季常青，具有较高的观赏价值。耐寒性较强，适应性强，适合庭院孤植或做绿篱使用，也可作为行道树栽培。喜阳光充足的环境，对土壤要求不严，养护相对简单。</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1822,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>蓝莓是杜鹃花科越橘属的落叶灌木植物，喜酸性疏松土壤，需充足光照。结果期需保持土壤湿润，但忌积水。果实富含花青素和维生素，具有较高的营养价值和保健功能。一号蓝莓是该品牌的优质品种，生长势强，适应性广，适合庭院地栽或盆栽种植。种植时需注意人工授粉以提高坐果率。</t>
+          <t>虹安果树蓝莓一号是蓝莓品种，果树属于灌木类植物。蓝莓果实富含花青素，具有保护眼睛、增强免疫力等功效。一号蓝莓品种适合家庭园艺种植，喜酸性土壤，需充足阳光，果实成熟期适中，产量稳定。种植时需注意保持土壤酸性（pH值4.5-5.5），定期施肥，适时修剪枝条以促进新枝生长和结果。</t>
         </is>
       </c>
     </row>
@@ -1860,11 +1862,9 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>帝罗马圆型托盘红陶款，采用优质红陶材质，经高温烧制而成，透气性好，适合搭配各种帝罗马品牌的花盆使用。圆型设计稳固牢靠，可有效收集多余水分，防止浇水时弄湿地面，同时保持植株根部良好的通气排水环境。红陶材质质感自然朴拙，具有良好的装饰效果，适用于家庭园艺、阳台花园、室内绿植等多种场景，是花卉盆栽的理想配件。</t>
+          <t>帝罗马红陶圆型托盘是一款经典园艺配件，采用意大利优质红陶材质制成，质感粗糙自然，透气性好。圆形设计适合搭配各类帝罗马品牌花盆使用，底部平整稳固，可有效收集多余水分，防止浇水时弄湿地面，同时增加花盆稳定性。红陶材质经过高温烧制，耐候性强，适合室内外各种园艺场景使用，是提升盆栽整体美观度的理想选择。</t>
         </is>
       </c>
     </row>
@@ -1899,14 +1899,9 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>GZ</t>
-        </is>
-      </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>小青柠</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1916,7 +1911,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>花叶小青柠是芸香科柑橘属的矮生灌木品种，因叶片带有斑纹而得名，成年植株高度在1-2米左右。叶片深绿带黄色斑块，边缘有锯齿，具有较高的观赏价值。春季开白色小花，夏季结果，果实小而圆，成熟时呈金黄色，酸甜可口。适合庭院种植或盆栽观赏，既可作为观叶植物点缀空间，又可收获果实。喜阳光充足的环境，耐半阴，土壤要求疏松肥沃、排水良好。</t>
+          <t>花叶小青柠是柑橘类观叶植物，叶片带有黄色斑纹，色彩明亮。植株为常绿灌木，果实为青柠，芳香怡人。适合庭院种植或盆栽观赏，喜阳光充足的环境，需要定期修剪保持株型美观。</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1963,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>寒香蜜是葡萄的一个优良品种，属于欧美杂交种。果实呈紫红色，颗粒饱满，香甜可口，具有浓郁的蜂蜜香味。该品种适应性强，抗病性好，适合家庭园艺种植。作为藤本植物，需要搭架栽培，喜欢充足的光照和通风环境。对土壤要求不严，但以排水良好的沙质土壤为佳。花果期需要适当疏花疏果，以保证果实品质。</t>
+          <t>寒香蜜是近年引进的欧美杂交种葡萄品种，果穗紧凑圆锥形，平均穗重400-600克，果粒椭圆形，成熟时呈黄绿色或淡粉红色。该品种最大的特点是丰产性强、抗病性好，非常适合新手种植。懒人葡萄系列的特性在于管理简便、修剪容易，适合庭院种植或阳台盆栽。成熟期在8月中下旬，果实香甜可口，带有淡淡的玫瑰香味。种植时需搭设简易棚架，保持充足光照和通风。</t>
         </is>
       </c>
     </row>
@@ -2008,11 +2003,9 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>帝罗马品牌圆型托盘，摩卡色系，11寸规格。采用优质环保材料制作，耐磨耐用，质感细腻。与帝罗马花盆配套使用，用于承接排水、保持地面清洁，也可作为浇水托盘。经典的摩卡色调简约大方，适合各种园艺风格搭配，是室内外绿植养护的实用配件。</t>
+          <t>帝罗马圆型托盘摩卡11是一款经典的园艺盆器配件，采用高品质陶土材质制作，质感细腻。该托盘为圆形设计，可有效收集花盆底部多余的水分，防止浇水时弄湿地面或家具，同时保持植物根系透气。摩卡色系典雅大方，适合各种室内外园艺场景搭配使用，提升整体园艺空间的装饰美感。</t>
         </is>
       </c>
     </row>
@@ -2034,17 +2027,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>园艺周边</t>
+          <t>工具</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>装饰摆件</t>
+          <t>清洁工具</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>装饰摆件</t>
+          <t>清洁工具</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2052,11 +2045,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>花彩师品牌园艺毛巾，专为园艺爱好者设计的清洁用品。橙色配色明亮活泼，适用于花园、阳台等园艺场景使用。可用于擦拭花盆、清洁园艺工具或日常清洁。材质柔软吸水，耐用易清洗，是园艺操作的实用辅助工具。</t>
+          <t>花彩师园艺毛巾是一款专为园艺爱好者设计的清洁工具，采用柔软吸水性面料制作，可用于擦拭植物叶片、清洁花盆、清理园艺工具等。橙色设计时尚醒目，便于识别和查找。质地耐用、不掉毛絮，可重复清洗使用，是日常园艺养护的实用辅助用品。</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2099,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>白玉枇杷是枇杷中的优质早熟品种，果肉洁白如玉，口感细腻，甜度高，多汁味美。枇杷树为常绿乔木，树形优美，叶片浓绿有光泽，具有较高的观赏价值。该品种适应性强，喜温暖湿润气候，耐寒性较好，适合种植于阳光充足、排水良好的微酸性土壤中。枇杷果实营养丰富，既可直接鲜食，也可制作成果酱、果汁等加工品，同时枇杷叶具有清肺止咳的药用功效，集食用、药用、观赏于一体。</t>
+          <t>白玉枇杷是枇杷的白色果肉品种，树形优美，四季常绿，观赏价值高。果实呈淡黄色或白色，果肉细腻多汁，甜度高，口感佳。适合庭院、阳台或果园种植。喜温暖湿润气候，耐寒性一般，需选择阳光充足、排水良好的环境种植。成年树高可达3-5米，丰产性好，是优良的庭院果树品种。</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2126,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>专用介质</t>
+          <t>普通介质</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>花卉专用介质</t>
+          <t>其他普通介质</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2148,11 +2139,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>花彩师植物通用介质是专为家庭园艺设计的通用型种植土，容量15L，适用于各类花卉、蔬菜、果树等植物的盆栽种植。该介质采用科学配比，富含腐殖质和营养成分，透气性和保水性良好，能够为植物根系提供健康的生长环境。适用于室内外观赏植物的换盆、播种、扦插等多种用途，使用前建议先疏松土壤并适当浇水湿润。</t>
+          <t>花彩师植物通用介质是专为家庭园艺设计的通用型栽培介质，容量15L，适合种植各种室内外植物。该介质采用科学配比的营养基质，透气性好、保水性强，能为植物根系提供良好的生长环境。可直接用于盆栽植物的栽培或作为土壤改良材料使用，适用于花卉、蔬菜、草本植物等多种植物的种植需求。使用时可根据植物特性适量混合园土或其他介质使用。</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2168,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>乔木</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>其他乔木</t>
+          <t>其他灌木</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>虹安</t>
+          <t>虹安果树</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2204,7 +2193,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>虹安宝玉是一款早熟油桃品种，果实成熟期较早，果实表面光滑无毛，果肉金黄脆甜，汁多味美。该品种适应性强，易于管理，适合庭院种植或规模果园栽培。喜阳光充足的环境，土壤宜选择疏松肥沃、排水良好的沙质土壤。种植后需注意合理修剪，保持树形通风透光，适时施肥促进生长和结果。</t>
+          <t>虹安宝玉是虹安果树推出的早熟油桃品种，果实圆形或扁圆形，果皮光滑无毛，呈鲜红色或金黄色，果肉致密多汁、甜度高、风味佳。该品种早熟丰产性好，适应性强，耐贮运，适合我国大部分桃产区种植。树势中庸，萌芽力和成枝力较强，栽培管理相对简单，是优良的早熟油桃品种，适合庭院种植或规模果园发展。</t>
         </is>
       </c>
     </row>
@@ -2231,12 +2220,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>乔木</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>其他乔木</t>
+          <t>其他灌木</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2256,7 +2245,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>G蜜桔1号是蜜桔的优质品种，属于芸香科柑橘属常绿小乔木。果实呈扁圆形，果皮橙黄色，易剥皮，果肉细嫩多汁，甜度高，口感佳。该品种适应性强，耐寒性较好，适合在我国南方地区种植。树冠圆头形，生长势中等，株型紧凑，适合庭院种植或规模化果园栽培。喜阳光充足、温暖湿润的环境，适宜疏松肥沃、排水良好的土壤。需注意防治炭疽病、疮痂病等常见病害。</t>
+          <t>G蜜桔1号是柑橘类果树品种，具有适应性强、产量稳定等特点。果实皮薄汁多、甜度高，适合家庭庭院种植或规模化栽培。喜阳光充足、排水良好的环境，适宜生长温度15-30℃，需定期施肥和修剪以保证果实品质。</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2297,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>虹安进口金隐枫树是荷兰精选的高端观叶枫树品种，金隐以其色彩艳丽的金黄色叶片著称，春季新叶呈金橙色，夏季转为黄绿色，秋季变为橙红色，色彩层次丰富。该品种株型紧凑，适合庭院种植、盆栽观赏或作为景观节点植物。喜半阴环境，耐寒性较好，排水良好的土壤有利于其健康生长。</t>
+          <t>虹安进口枫树金隐品种，源自荷兰2025年新到货品。D级苗龄规格，植株健壮，根系发达。金隐是经典的日本枫树品种，叶色金黄璀璨，春季新叶呈明亮的金黄色，夏季转为黄绿色，秋季转为橙红色，色彩层次丰富。树形优雅，枝叶舒展，适合庭院孤植、列植或组合盆栽观赏。喜半阴环境，避免强光直射，适宜疏松排水良好的微酸性土壤，生长季节保持水分充足，冬季适当控水。</t>
         </is>
       </c>
     </row>
@@ -2348,11 +2337,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>花彩师鸡牛羊三合一有机肥是以鸡粪、牛粪、羊粪为原料，经过科学配比和充分发酵腐熟制成的有机肥料。产品富含有机质、氮磷钾及微量元素，能有效改善土壤结构，增加土壤透气性和保水性。适用于家庭园艺各类植物的底肥和追肥使用，可广泛用于蔬菜、果树、花卉、草坪等的种植养护。使用时建议与土壤混合或作基肥施入，注意避免直接接触植物根系。</t>
+          <t>花彩师鸡牛羊三合一有机肥是一款以鸡粪、牛粪、羊粪为原料科学配比而成的有机肥料产品。产品为颗粒状有机肥，净含量900g，适合用于家庭园艺各类植物的基肥或追肥使用。三合一配方综合了不同动物粪便的营养优势，富含有机质和植物所需的氮磷钾等营养元素，能够改善土壤结构，增加土壤肥力，促进植物健康生长。适用于花卉、蔬菜、果树等多种园艺植物，使用时建议按照植物需求和土壤情况适量施用，避免直接接触根系。</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2376,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>安酷</t>
+          <t>HY-安酷</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,7 +2391,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>安酷杜鹃“豆蔻”是安酷系列（Encore Azaleas）中的一个优秀品种，以其重复开花特性著称。该品种株型紧凑，花朵呈淡粉色或豆蔻色系，花期较长，可多次开花。耐寒性较好，适应性强，适合庭园点缀、灌木边界或盆栽观赏。喜酸性、疏松排水良好的土壤，喜半阴环境，需适当修剪维护良好株型。</t>
+          <t>安酷杜鹃“豆蔻”是一款经典的杜鹃花品种，花朵呈淡粉色或粉紫色，重瓣或半重瓣，花期通常在春季。安酷系列杜鹃以其丰花性和良好的适应性著称，适合用于庭院景观、花园点缀或盆栽观赏。该品种喜酸性、疏松排水良好的土壤，喜半阴环境，忌阳光直射，耐寒性较好。生长速度中等，成年株高可达1-1.5米，适合做花境前景或丛植配置。</t>
         </is>
       </c>
     </row>
@@ -2444,11 +2431,9 @@
           <t>Jay</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>椰糠颗粒是一种天然有机栽培介质，由椰子外壳纤维加工而成。具有良好的透气性、保水性和排水性，pH值呈弱酸性至中性，适合大多数园艺植物生长。可单独作为栽培基质使用，也可与其他介质（如泥炭土、珍珠岩等）混合使用，改善土壤结构。适用于盆栽植物、花卉、蔬菜育苗等场景，能促进根系发育，是现代园艺中广泛使用的环保型介质。</t>
+          <t>200L椰糠颗粒是一种常见的园艺栽培介质，由椰子外壳加工而成。具有良好的透气性、保水性和排水性，EC值低，pH值适中，呈弱酸性至中性。颗粒状结构便于与珍珠岩、泥炭等介质混合使用，适用于多肉植物、兰花、观叶植物等各类盆栽植物的种植。可单独使用或作为土壤改良材料，能有效改善土壤结构，促进植物根系生长发育。</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2485,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>彩虹梨"擎天柱"是虹安果树推出的特色梨树品种，果皮呈彩色，果实汁多味甜，具有较高的观赏价值和食用价值。该品种树势旺盛，适应性广，耐寒耐热，适合庭院种植或规模化果园栽培。栽植时应选择阳光充足、排水良好的环境，春季开花结果，秋季采收。需注意合理修剪和施肥，促进植株健康生长，提高果实品质。</t>
+          <t>彩虹梨"擎天柱"是虹安果树品牌推出的特色梨树品种，果皮呈现红黄渐变的彩虹色泽，外观艳丽，观赏价值高。该品种树势中庸，适应性广，耐寒性较强。果实脆甜多汁，口感好，既可食用又具观赏性。适合庭院种植或规模化果园栽培，喜阳光充足、排水良好的土壤环境，需注意适时修剪和病虫害防治。</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2537,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>阳光玫瑰是欧美杂交葡萄品种，果粒大、糖度高、带有浓郁玫瑰香味。植株为藤本植物，需要搭架栽培，喜阳光充足的环境，适应性较强。果实成熟期一般在夏秋季，适合庭院种植或规模化果树栽培，是近年来受欢迎的鲜食葡萄品种。</t>
+          <t>阳光玫瑰是近年来备受欢迎的葡萄新品种，果粒呈黄绿色，晶莹剔透，口感脆甜多汁，带有浓郁的玫瑰香气。该品种抗病性强、适应性好、丰产性强，果实耐储运，适合庭院种植或规模化栽培。喜阳光充足的环境，需搭架引蔓，保持通风透光，注重合理修剪和疏花疏果，以获得优质果实。</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2589,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>虹安枫树女神是一款优美的观叶乔木品种，2025年出货规格。枫树树姿优雅，春季新叶色彩鲜艳，夏季转为深绿色，秋季叶片变红或金黄，极具观赏价值。适合庭院孤植、群植或作为行道树，喜阳光充足或半阴环境，耐寒性较强，土壤要求排水良好。是园林景观中重要的彩叶乔木品种。</t>
+          <t>虹安枫树“女神”是一款观赏价值极高的落叶乔木品种，树形优美，枝叶繁茂。春季新叶呈嫩绿色，夏季叶片浓绿，秋季变为鲜艳的橙红色或金黄色，色彩艳丽，观赏期长。适合庭院孤植、群植或作为行道树，能够营造优美的园林景观效果。性喜阳光充足的环境，耐寒性较强，适宜种植在疏松肥沃、排水良好的土壤中。养护时注意保持土壤湿润，避免积水，并适当修剪以保持良好树形。</t>
         </is>
       </c>
     </row>
@@ -2644,11 +2629,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>花彩师园艺粘虫板是一款常用的植物保护工具，采用粘性材料制成，用于诱捕和粘杀温室、大棚及户外园艺环境中的害虫，如蚜虫、白粉虱、斑潜蝇、蓟马等小型飞行昆虫。16片装设计，方便用户根据种植面积灵活使用。使用时将粘虫板悬挂在植物上方或周围，定期检查并更换即可，有效减少农药使用，绿色环保，适用于家庭园艺、蔬菜种植、花卉养护等多种场景。</t>
+          <t>花彩师园艺粘虫板是一款高效的物理灭虫工具，采用黄色粘虫板设计，利用害虫对黄色的趋性进行诱捕。可有效防治蚜虫、白粉虱、斑潜蝇、果蝇等多种园艺害虫。16片装设计，适合家庭园艺、温室大棚、果蔬种植等多种场景使用。绿色环保，无需使用农药，安全无毒。使用时将粘虫板悬挂于植株上方或周围，定期更换即可。使用简单方便，是生态园艺、有机种植的理想选择。</t>
         </is>
       </c>
     </row>
@@ -2670,17 +2653,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>种苗苗木</t>
+          <t>球块茎</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>多年生草本</t>
+          <t>鳞茎</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>其他多年生草本</t>
+          <t>其他鳞茎</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2700,7 +2683,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>百子莲原产南非，别名非洲百合、君子兰，是石蒜科多年生草本植物。烟花是该品种的商品名，花型优雅、花色鲜艳、开花繁茂。喜阳光充足、温暖湿润的环境，耐热耐寒，适应性强。适合庭院花境、阳台盆栽或切花观赏。花期夏秋季节，伞形花序可开放数十朵小花，观赏价值高。进口种苗品质优良，栽培难度较低，适合家庭园艺爱好者种植。</t>
+          <t>百子莲（Agapanthus）是一种多年生球根植物，进口品质，花朵呈漏斗状，伞形花序，原产南非。'烟花'是该品种的商品名，花色独特，盛开时如烟花般绚烂。喜阳光充足、排水良好的环境，耐寒性较好。适合庭院花境、岩石园或盆栽观赏，花期主要在夏季。作为鳞茎植物，种植深度以鳞茎顶部与土面平齐为宜，保持土壤湿润但避免积水。</t>
         </is>
       </c>
     </row>
@@ -2745,14 +2728,9 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>大花绣球</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>安镇大花绣球多株混苗是一款绣球花苗木产品，绣球花为落叶灌木，花团锦簇、花色丰富，常见蓝、紫、粉、白等色，大花绣球品种花序较大、观赏价值高。该苗木适合庭院种植或盆栽观赏，喜半阴环境，不耐强光直射，喜疏松肥沃、排水良好的土壤。生长期需保持土壤湿润，但忌积水。冬季适当控水，北方地区需注意防寒保护。花期一般在5-8月，可通过调节土壤酸碱度改变花色。</t>
+          <t>安镇大花绣球多株混苗是绣球花苗木组合，株型饱满，花朵大而饱满，颜色丰富绚烂。该品种属于落叶灌木，株高一般在60-150厘米，适合庭院种植、花境配置或盆栽观赏。喜半阴环境，不耐强光直射，喜肥沃湿润、排水良好的土壤。春季萌芽后需补充养分，花后及时修剪残花，保持植株美观。越冬时注意防寒保暖，是广受欢迎的观花灌木品种。</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2767,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HY-安酷</t>
+          <t>安酷</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2804,7 +2782,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>安酷杜鹃“康乃馨”是一款优秀的灌木花卉品种，花朵呈粉红色，形似康乃馨般优雅动人。该品种植株紧凑，分枝性好，株型丰满，适合庭院种植或盆栽观赏。花期较长，观赏价值高。喜酸性土壤，喜半阴环境，怕强光直射。耐寒性较好，适应性较强，适合我国大部分地区种植。栽培时应保持土壤湿润但避免积水，定期施用酸性肥料以维持土壤pH值在5.5-6.0之间。</t>
+          <t>安酷杜鹃“康乃馨”是一款优秀的常绿灌木品种，花朵呈康乃馨粉色，重瓣大花，春季盛开时花量丰富，观赏价值极高。植株生长紧凑，株型丰满，适应性强，耐寒耐热，适合庭院种植或盆栽观赏。喜欢酸性土壤和半阴环境，需保持土壤湿润但避免积水。</t>
         </is>
       </c>
     </row>
@@ -2841,14 +2819,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>虹越</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>虹越定制</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>虹越定制短款防刺手套，专为园艺爱好者设计的手部防护用品。短款设计方便灵活操作，防刺功能有效保护手部免受植物刺伤和划伤。适用于修剪、嫁接、种植等园艺操作场景，佩戴舒适，操作便捷，是从事园艺活动时的基础防护工具。</t>
+          <t>短款防刺手套，专为园艺操作设计，采用耐磨防刺材质，有效保护手部免受玫瑰、月季等带刺植物的伤害。短款设计便于灵活操作，适合日常园艺养护、修剪、换盆等场景使用，是园艺爱好者的必备防护工具。</t>
         </is>
       </c>
     </row>
@@ -2888,11 +2864,9 @@
           <t>虹越定制</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>这是一款1.5L容量的直头气压喷壶，采用复古蓝色设计，适合家庭园艺浇水使用。气压式设计方便喷雾，可用于浇灌花卉、喷洒叶面、调节空气湿度等。直头设计出水集中，适合精准浇灌小盆栽或花卉根部。复古色调兼具实用性与装饰性，是园艺爱好者日常养护的好帮手。</t>
+          <t>虹越定制直头气压喷壶，容量1.5L，复古蓝色外观。气压式设计便于均匀喷洒，内置打气装置可产生持续稳定的水压，直头设计适合精准浇灌植物根部或叶片。适用于家庭园艺、小型盆栽浇水使用，轻巧便携，操作简便，是园艺爱好者日常养护的实用工具。</t>
         </is>
       </c>
     </row>
@@ -2932,11 +2906,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>花彩师球根植物专用介质是专为球根类花卉研发的栽培基质，容量为3.5L。介质配方针对球根植物的生长特性设计，透气性和排水性优良，有利于球根的生长发育和开花。适用于郁金香、朱顶红、百合、风信子等球根花卉的种植，能够提供良好的根系环境，促进球根快速生根，减少烂球风险。使用时可根据球根大小和容器规格适量添加，建议保持介质微润但不过湿。</t>
+          <t>花彩师球根植物专用介质是专为球根类花卉研发的栽培基质，容量3.5L。采用优质泥炭、珍珠岩等材料科学配比，具有良好的透气性和排水性，富含球根生长所需营养物质。适用于郁金香、朱顶红、风信子、百合等球根植物的种植和栽培。能有效防止球根积水烂根，促进根系健康生长，是球根植物播种、换盆的理想选择。</t>
         </is>
       </c>
     </row>
@@ -2976,11 +2948,9 @@
           <t>花逸乐</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>花逸乐海藻有机颗粒肥是一种以深海海藻为主要原料的有机肥料，富含天然植物生长素和微量元素。有机颗粒状设计，肥效释放缓慢持久，适合各类花卉、蔬菜、果树及盆栽植物使用。施用方便，可做基肥或追肥，能有效改善土壤结构，增加土壤有机质含量，促进植物根系发育和营养吸收。2.5kg包装适合家庭园艺使用，注意避免直接接触植物根部，施用后适量浇水以促进肥效释放。</t>
+          <t>花逸乐海藻有机颗粒肥是一款以天然海藻为主要原料的有机肥料，富含植物生长所需的多种微量元素和活性物质。颗粒状设计便于均匀撒施，适用于家庭园艺中各类花卉、蔬菜、果树的基肥和追肥使用。有机成分改良土壤结构，增加土壤透气性和保水性，促进根系发育，提高植物抗病抗逆能力。2.5kg规格适合中小型庭院或阳台园艺使用，安全环保，适合有机种植需求。使用时建议按照植物种类和生长阶段适量施用，避免直接接触植物根部。</t>
         </is>
       </c>
     </row>
@@ -3020,11 +2990,9 @@
           <t>奥石克莱尔</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>奥石克莱尔圆型两用种植盆，采用优质塑料材质制作，质地坚固耐用，具有良好的抗老化性能。圆形设计简洁大方，可用于室内桌面或室外庭院摆放。两用功能设计既可直接种植，也可作为套盆使用。黑色配色经典百搭，易于清洁打理。盆体透气透水孔设计合理，利于植物根系呼吸和水分排出，适合种植各类草本花卉、多肉植物、小型灌木等。建议日常使用避免长期暴晒，定期清理盆面积尘，可延长使用寿命。</t>
+          <t>奥石克莱尔圆型两用种植盆，黑色经典配色，简约大气。采用优质塑料材质，轻便耐用，耐候性强。圆型设计适合多种植物种植，两用功能可用于土培或作为套盆使用，底部设有排水孔设计，透气性好，便于根系呼吸。口径17cm，适合中小型植物栽培使用，是家庭园艺的理想选择。</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3019,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>通用肥</t>
+          <t>特肥</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>水溶肥</t>
+          <t>其他特肥</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3064,11 +3032,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>花彩师浓缩营养液天南星科型是一款专为天南星科植物（如龟背竹、绿萝、红掌、白掌等）设计的液态肥料。产品采用高浓度浓缩配方，富含氮磷钾及微量元素，使用时需稀释后浇灌或叶面喷施。该产品能促进天南星科植物叶片生长，增强叶色光泽，提高抗病能力。250ml包装便于储存和使用，适合家庭园艺爱好者为室内观叶植物补充营养。</t>
+          <t>花彩师浓缩营养液（天南星科型）是一款专用液体肥料，规格250ml，专为天南星科植物（如龟背竹、绿萝、红掌、白掌、滴水观音等）研发配制。富含氮磷钾及微量元素，配方针对性强，能有效促进天南星科植物叶片生长，使叶色更加翠绿光亮。浓缩液体需稀释后使用，适合家庭园艺养护。使用时按说明比例兑水，浇灌或叶面喷施均可，建议在植物生长期每7-14天施用一次。</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3086,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>蜜桔一号是柑橘类早熟优良品种，树姿半开张，枝条细长且具刺，叶片椭圆形或卵状椭圆形。果实扁圆形，果皮橙黄色或深橙色，易剥离，果肉细嫩多汁，甜酸适口，品质优良。适合庭院种植或果园规模栽培，喜温暖湿润气候，需充足阳光照射，土壤以疏松肥沃、排水良好的酸性至微酸性土壤为宜。移栽后注意保持土壤湿润，适当修剪整形，促进树冠通风透光，提高坐果率。</t>
+          <t>蜜桔是常绿小乔木或灌木，原产中国，果实呈扁圆形，成熟时呈橙红色，果肉多汁甜美，酸甜适中。该品种适应性强，耐寒性较好，适合庭院种植或规模化栽培。蜜桔喜阳光充足、排水良好的环境，适宜在微酸性至中性土壤中生长。花期4-5月，果期10-12月。种植时需注意合理修剪，保持通风透光，及时施肥管理，以提高果实品质和产量。</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3126,9 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>帝罗马经典宽边高圆型盆白陶22是一款高品质园艺花盆，采用优质白陶材质制作，质地细腻坚固，透气性好。宽边设计不仅美观大方，还方便日常浇水换土操作。高圆型盆身适合种植各类中小型植物，22CM的尺寸可满足多种场景使用需求。该花盆造型经典优雅，适合室内外阳台、庭院等多种环境摆设，是追求品质的园艺爱好者的理想选择。</t>
+          <t>帝罗马经典宽边高圆型盆，采用优质白陶材质制作，工艺精湛，质感细腻。宽边设计不仅美观大方，还方便搬运和换盆操作。高圆型盆身设计提供了充足的根系生长空间，适合种植各类中小型植物，如多肉、绿植、花卉等。白陶材质透气性好，有利于植物根系呼吸，同时具有较好的保水性。经典款式适用于家居装饰、阳台园艺、花店陈列等多种场景，兼具实用性与装饰性。</t>
         </is>
       </c>
     </row>
@@ -3201,12 +3165,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>安酷</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>安酷杜鹃</t>
+          <t>杜鹃</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3216,7 +3180,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>安酷杜鹃‘美人’是日本Azuma公司培育的安酷系列杜鹃花品种之一。安酷系列以其大花、重瓣、花色丰富艳丽而著称。‘美人’品种花色粉红或玫红色调，花型优美，观赏价值高。该品种株型紧凑，生长势强健，适应性强，耐寒耐热，适合庭院种植或盆栽观赏。花期通常在春季，盛花时花团锦簇，具有极高的园林装饰效果。</t>
+          <t>安酷杜鹃“美人”是HY公司推出的安酷系列杜鹃花品种。花朵呈粉红色，重瓣勤花，具有多季开花特性，株型紧凑圆润，观赏价值高。适合庭院种植、花园景观布置或盆栽观赏。喜酸性疏松土壤，喜半阴环境，需保持湿润但忌积水。</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3227,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>响声</t>
+          <t>响声XQZ</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>大花绣球响声是一种迷人的绣球花品种，花朵大而丰满，花期通常在春末夏初，花色丰富多变，具有极高的观赏价值。适合种植于庭院、花坛或作为盆栽观赏。喜半阴环境，不耐强光直射，喜欢疏松肥沃、排水良好的酸性土壤。养护时需保持土壤湿润但避免积水，冬季注意防寒修剪，可适当施肥促进开花。</t>
+          <t>大花绣球响声XQZ是绣球花的一个品种，具有大而美丽的球形花序，花色丰富多变，通常在春夏季开花。该品种适应性较强，喜欢半阴环境，适合种植于庭院、花园或盆栽中。绣球花需保持土壤湿润，但避免积水，喜肥沃疏松的土壤。在养护过程中需注意适当修剪，以促进新枝生长和花芽形成。</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3284,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>大花绣球露娜是绣球花的优良品种，以大花著称，花球饱满硕大，观赏价值极高。该品种适应性强，耐半阴环境，适合庭院种植或盆栽观赏。花色可随土壤酸碱度变化，酸性土壤呈蓝色，碱性土壤呈粉红色。养护需保持湿润环境，避免强光直射，冬季适当修剪枯枝，春季追肥促进开花。</t>
+          <t>大花绣球露娜是绣球花的一个品种，花朵大而饱满，色彩丰富艳丽，具有很高的观赏价值。绣球花属于灌木类植物，喜半阴环境，不耐强光直射，喜欢疏松肥沃、排水良好的土壤。该品种适合种植于庭院、花坛或盆栽中，花期通常在春末夏初，盛开时花团锦簇，是园林绿化和家庭园艺中常见的观赏花卉。养护时需注意保持土壤湿润，避免积水，冬季需适当防寒。</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3331,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>早熟油桃</t>
+          <t>虹安黛玉</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>虹安黛玉早熟油桃是虹安果树品牌推出的优质油桃品种。该品种具有早熟特性，果实表面光滑无毛，果肉金黄脆甜，风味独特。适合庭院种植或果园规模栽培，喜欢阳光充足、排水良好的环境。种植时需注意合理修剪，保持通风透光，定期施肥以促进果实发育和品质提升。</t>
+          <t>早熟油桃品种，树势中庸，树姿半开张，果实圆形或扁圆形，果皮光滑无毛，呈橙红色，果肉黄色，汁多味甜，香味浓郁。该品种丰产性好，适应性强，耐贮运，适合庭院种植或规模栽培。喜阳光充足、排水良好的环境，适宜在微酸性至中性土壤中生长。种植时应注意合理修剪，保持树冠通风透光，加强肥水管理，以提高果实品质。</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3388,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>树莓是蔷薇科悬钩子属多年生灌木果树，果实色泽鲜亮、酸甜可口，富含维生素和花青素，具有较高的营养价值和药用价值。该品种虹安挚爱是丰产性较好的树莓品种，适应性强，耐寒耐旱，适合庭院种植或规模化栽培。树莓喜欢阳光充足的环境，土壤以疏松肥沃、排水良好的微酸性土壤为佳。栽植后需保持土壤湿润，定期施肥修剪，以促进新枝萌发和果实产量提升。</t>
+          <t>虹安挚爱树莓是灌木类果树，植株高度中等，分枝性好，果實呈鲜红色，酸甜可口，營養豐富。適合庭院種植或盆栽觀賞，既能觀花又能採果。喜陽光充足的環境，耐寒性較強，對土壤適應性廣，但以疏鬆肥沃、排水良好的土壤為佳。種植後保持土壤濕潤，避免積水，並注意定期施肥以促進結果。</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3430,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>大花绣球</t>
+          <t>绣球</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3476,7 +3440,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>大花绣球“露娜”是一款优质的绣球花品种，花朵大而丰满，观赏价值高。该品种适应性强，适合庭院种植或盆栽观赏，喜欢半阴环境，需保持土壤湿润。绣球花可通过调节土壤酸碱度改变花色，是深受园艺爱好者喜爱的经典花卉品种。</t>
+          <t>安镇大花绣球“露娜”是一款灌木型绣球花品种，花朵大而饱满，观赏价值高。该品种适合庭院种植或盆栽观赏，喜半阴环境，不耐强光直射。土壤宜选择疏松肥沃、排水良好的微酸性土壤。生长期需保持充足的水分供应，但避免积水。冬季可适当修剪残花和枯枝，促进来年开花。绣球花色可随土壤酸碱度变化而呈现不同色调，是广受欢迎的观赏花卉品种。</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3477,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>虹越</t>
+          <t>虹越植物</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3528,7 +3492,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>落叶杜鹃是杜鹃花科落叶灌木植物，秋季落叶，春季先花后叶。"安娜"是该品种的商品名称，花色艳丽，花期较早，观赏价值高。适合庭院种植或盆栽观赏，喜酸性土壤和半阴环境，需适当修剪维护株型，花后及时补充养分利于来年开花。</t>
+          <t>落叶杜鹃“安娜”是一款优雅的落叶灌木花卉，春季开花，花朵呈粉色或淡紫色，层层叠叠，极具观赏价值。该品种株型紧凑，枝条优美，适合庭院孤植或群植配置。性喜阳光充足、排水良好的环境，略耐寒。落叶杜鹃开花繁茂，花期较早，是早春园林中重要的观花灌木，可与其他灌木搭配营造丰富的景观层次。养护需注意保持土壤酸性，适时修剪以维持良好株型。</t>
         </is>
       </c>
     </row>
@@ -3568,11 +3532,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>花彩师家庭园艺植物精油防护剂是一款用于家庭园艺植物保护的护理产品，采用植物精油配方，可帮助植物抵御病虫害侵袭。产品为补充装设计，容量480ml，适合家庭园艺爱好者使用。使用时按照说明稀释后喷洒于植物叶面及茎部即可，有助于保持植物健康生长，减少化学农药的使用。</t>
+          <t>花彩师家庭园艺植物精油防护剂补充装480ml，是一款用于家庭园艺植物防护的精油类护理产品。主要成分为植物精油提取物，可用于防治常见园艺植物害虫，如蚜虫、红蜘蛛、介壳虫等。采用天然植物成分，温和环保，适合家庭园艺使用。补充装设计便于后续添加使用，经济实惠。使用时建议按比例稀释后均匀喷洒于植物叶面及茎秆，避开强光高温时段。产品需存放在阴凉干燥处，避免儿童接触。</t>
         </is>
       </c>
     </row>
@@ -3612,11 +3574,9 @@
           <t>奥石克莱尔</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>奥石克莱尔圆型两用种植盆，采用优质塑料材质制成，圆形设计美观大方，具备浇水盘和排水孔双重功能。17寸规格适合种植中小型花卉、蔬菜及多肉植物等。叶绿色配色清新自然，适合室内外园艺使用。盆壁加厚设计，耐用且便于搬运移动。</t>
+          <t>奥石克莱尔圆型两用种植盆，采用叶绿色配色设计，圆形盆体造型美观大方。两用设计可适用于不同种植需求，既可用于花卉栽培，也可用于蔬菜种植。盆体材质坚固耐用，排水性能良好，适合家庭园艺使用。17cm的尺寸规格适中，适合种植中小型植物，是阳台、窗台园艺的理想选择。</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3628,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>蓝莓“天后”是一种高品质的蓝莓品种，果实大而饱满，甜度高，风味浓郁。该品种适应性较强，适合家庭园艺种植。蓝莓喜酸性土壤（pH值4.5-5.5），需要充足的阳光和良好的排水条件。种植时应选择透气性好的介质，定期施用酸性肥料。生长期需要保持土壤湿润但避免积水。蓝莓结果后可鲜食或用于制作果酱、果汁等，具有较高的营养价值。</t>
+          <t>蓝莓“皇后”是一种早熟高产的蓝莓品种，植株长势旺盛，果实个大饱满，果粉浓厚，风味香甜。该品种适应性强，耐寒性较好，适合我国大部分地区种植。果实成熟期较早，可提早上市，经济效益较高。蓝莓需酸性土壤栽培（pH值4.5-5.5），喜阳光充足，排水良好的生长环境。适合庭院种植或果园规模化栽培，既可观花又可采果，具有较高的观赏价值和食用价值。种植时需注意配置授粉树以提高坐果率。</t>
         </is>
       </c>
     </row>
@@ -3710,17 +3670,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>南方枸杞</t>
+          <t>枸杞</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>泡泡仙子</t>
+          <t>泡泡仙子/南方枸杞</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>南方枸杞是适合南方地区种植的枸杞品种，泡泡仙子为其特色品种。该品种株型适中，枝条柔软易修剪，适合庭院种植或盆栽。果实为红色小枸杞，具有观赏与食用双重价值。花期春夏季，花朵小巧淡雅。喜阳光充足的环境，耐热耐湿，对土壤要求不高，但以排水良好的沙质土壤为佳。养护时注意适当修剪，保持通风透光，减少病虫害发生。</t>
+          <t>虹安果树泡泡仙子和南方枸杞是枸杞品种的果苗。枸杞为落叶灌木，株型紧凑，适合庭院种植或盆栽观赏。果实可鲜食或晒干食用，具有较高的营养价值。喜阳光充足的环境，耐旱性强，对土壤要求不高，适宜在排水良好的土壤中生长。春季开花，夏季结果，秋季叶色转红，具有较高的观赏价值。</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3732,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>懒人葡萄“寒香蜜”是一款适合新手栽培的葡萄品种，具有管理简便、适应性强等特点。该品种果实香甜，口感好，产量稳定。适合庭院种植或盆栽，需搭架栽培，保持充足光照和通风。生长期间注意合理修剪和施肥，休眠期适当控水。对土壤要求不严，以疏松肥沃、排水良好的土壤为佳。</t>
+          <t>懒人葡萄“寒香蜜”是一款专为家庭园艺打造的低维护葡萄品种。植株生长势中等，适应性强，管理简便，适合新手栽培。果实成熟期早，果粒饱满，香味浓郁，口感甘甜多汁。适合庭院、阳台或露台种植，可搭设简易棚架让其攀爬生长，既能观赏绿荫又能品尝鲜果。喜阳光充足的环境，需定期浇水施肥，注意防治病虫害。</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3784,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>虹安枫树混品种是一类观赏价值极高的乔木植物，以其独特的掌状叶片和丰富多变的秋色著称。叶片在春季呈现嫩绿或紫红色，秋季则变为鲜艳的橙红、黄色或深红色，具有极高的园林景观价值。性喜阳光充足、通风良好的环境，耐寒性较强，适应性广，适合庭院孤植、丛植或作为行道树。养护时需注意保持土壤湿润但不积水，夏季适当遮阴，冬季可耐低温。混品种设计可满足不同用户对叶色、树形的个性化需求。</t>
+          <t>虹安枫树混品种是常见的观赏乔木苗木，枫树叶片秋季变为鲜艳的红色、橙色或黄色，具有极高的观赏价值。品种混搭种植可增加庭院的色彩层次感。性喜温暖湿润的环境，耐半阴，适应性强，适合庭院、公园、景区等场所种植观赏。秋季是最佳观赏期，养护时需注意适当修剪和施肥。</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3836,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>紫菀是一种多年生草本宿根植物，属菊科紫菀属。'秋语'是该品种的中文名称，寓意其在秋季绽放的优雅姿态。该品种株型紧凑，花色鲜艳，花期主要集中在秋季，能够为花园增添丰富的色彩层次。紫菀喜阳光充足、排水良好的环境，适应性强，耐寒性较好，适合用于花境、庭园边缘或容器栽培。养护时需注意避免积水，适度修剪可促进分枝和开花。</t>
+          <t>紫菀'秋语'是秋季开花的多年生宿根草本植物，属于菊科紫菀属。株型紧凑，花量丰富，花色通常为紫色或蓝紫色，花期集中在9-11月，是秋季花园重要的观赏花卉。喜阳光充足或半阴环境，适应性强，耐寒性较好。适合花境前景、边缘地带或盆栽观赏，可与秋季其他花卉搭配种植，营造丰富的色彩层次。养护简单，适合新手园艺爱好者。</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3888,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>脆皮金桔是金桔的优良品种，果皮薄脆、口感清甜无辛辣味。植株为常绿灌木或小乔木，株型紧凑美观，枝叶繁茂，既可观花观果也可食用。果实成熟后呈金黄色，挂果期长，适合阳台盆栽或庭院地栽种植。喜欢阳光充足、通风良好的环境，较耐寒，需注意疏花疏果以保证果实品质。</t>
+          <t>脆皮金桔是芸香科柑橘属的常绿灌木或小乔木，植株矮小紧凑，枝条细密。果实金黄呈圆球形，皮薄脆甜，果肉多汁，口感脆嫩无渣，甜度高而少酸涩。花期春季，白色小花芳香，果实秋冬季成熟。喜温暖湿润气候，需充足阳光，较耐寒，适应性强。对土壤要求不严，以疏松肥沃、排水良好的沙质壤土为佳。脆皮金桔既可观果又可食用，适合庭院种植、阳台盆栽或规模化果树栽培，具有较高的观赏价值和经济价值。</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3940,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>一号蓝莓是蓝莓品种中的优质品种，植株长势健壮，适应性强，适合家庭园艺种植。果实呈深蓝色，果肉细腻，酸甜可口，富含花青素，营养价值高。喜酸性土壤（pH值4.5-5.5），喜阳光充足的环境，需保持土壤湿润但忌积水。适合阳台、庭院盆栽或地栽，成年株高约1-1.5米，每年5-7月为成熟采收期。种植时需配置异花授粉品种以提高产量。</t>
+          <t>虹安果树蓝莓一号蓝莓是灌木类果树种苗，一号蓝莓为早熟品种，果实较大，果肉细腻，酸甜可口。该品种适应性强，适合我国大部分地区种植。蓝莓喜酸性土壤，需保持土壤疏松透气，生长期间需充足光照，浇水应遵循见干见湿原则。开花期需适当疏花，利于果实发育成熟。</t>
         </is>
       </c>
     </row>
@@ -4027,12 +3987,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>花叶奶茶</t>
+          <t>花叶奶茶R</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>小青柠是一种芸香科柑橘属的灌木类果树，植株较为紧凑，适合庭院种植或盆栽观赏。花叶奶茶是该品种的商品名，叶片可能具有特殊的斑纹或色彩。小青柠果实小巧圆润，成熟后呈青绿色，果肉酸甜多汁，富含维生素C，既可食用也可作为观赏植物。喜欢阳光充足的环境，耐半阴，适宜疏松肥沃、排水良好的土壤。生长季节需保持土壤湿润，但忌积水。冬季需注意防寒，北方地区建议盆栽室内越冬。</t>
+          <t>小青柠是柑橘类灌木植物，'花叶奶茶R'是一个观叶园艺品种，其叶片具有美丽的斑纹或特殊色彩，兼具观叶与观果价值。该品种株型紧凑，适合阳台盆栽或庭院种植，喜阳光充足的环境，需保持土壤湿润但忌积水，挂果期具有较高的观赏价值，适合家庭园艺爱好者种植。</t>
         </is>
       </c>
     </row>
@@ -4047,14 +4007,46 @@
           <t>虹安铁线莲 伊萨哥</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>藤本</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>虹安</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>伊萨哥</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>铁线莲伊萨哥是虹安品牌推出的藤本花卉品种，花型优美、花色鲜艳，具有较强的攀援能力，适合用于庭院棚架、墙面、篱笆等垂直绿化。该品种喜阳光充足、通风良好的环境，适宜种植在疏松肥沃、排水良好的土壤中。花期较长，观赏价值高，是打造花园景观的理想选择。养护时需注意保持土壤湿润但避免积水，定期施肥促进生长健壮。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4087,7 +4079,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>锦带</t>
@@ -4100,7 +4091,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>五彩锦带是锦带花的彩色品种，属落叶灌木，嫩枝淡红色，椭圆形叶片对生。其最大特点是花色绚丽多彩，同一植株上可见粉红、紫红、白色等多种花色，花期通常在春末夏初。五彩锦带喜光也耐半阴，适应性强，耐寒耐旱，对土壤要求不严，适合庭院种植或做花境材料，可孤植、丛植或列植。繁殖多用扦插或分株方法，养护相对简单，是观赏价值较高的园林灌木品种。</t>
+          <t>锦带-五彩锦带是锦带花的彩色叶变种，属落叶灌木。其最显著特点是叶片在生长季节呈现丰富的色彩变化，同一植株上有绿、白、粉、红等多种颜色，绚丽多彩。花期5-6月，花朵呈漏斗状，粉红色或玫瑰红色，密集成簇。植株高度约1-2米，冠幅相近，枝条拱形生长。喜阳光充足或半阴环境，适应性强，耐寒耐旱，对土壤要求不严。可孤植、丛植或作花篱，观赏价值高，适合庭院、公园等绿化布置。</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4123,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>花卉专用介质</t>
+          <t>花卉通用介质</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4140,11 +4131,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>花彩师花卉通用介质（粗颗粒）28L，是一款专为花卉植物设计的通用型栽培介质。粗颗粒配方具有良好的透气性和排水性，适合多肉、兰花等需要高透气性环境的花卉使用。介质经过科学配比，富含植物生长所需的基本养分，可直接用于播种、育苗或换盆换土使用。28L容量适中，适合家庭园艺爱好者日常种植需求。使用时应根据植物种类适当调整浇水频率，保持介质湿润但不过度积水。</t>
+          <t>花彩师花卉通用介质（粗颗粒）是一款专为花卉栽培设计的优质培养土，容量28L。粗颗粒配方具有良好的透气性和排水性，能有效防止盆土板结和积水烂根。适用于各类盆栽花卉的种植与换盆，如月季、绣球、铁线莲等。介质富含有机质和营养成分，可为植物根系提供良好的生长环境，促进花卉健康生长。使用时可根据植物需水量适当调整浇水频率。</t>
         </is>
       </c>
     </row>
@@ -4171,24 +4160,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>种植工具</t>
+          <t>基础工具</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>其他种植工具</t>
+          <t>基础工具</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>虹越定制</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+          <t>虹越</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>虹越定制园艺通用手套，专为园艺作业设计，采用墨绿色配色，耐磨耐用。手套采用优质材料制作，具有良好的透气性和防护性能，能够有效保护双手免受土壤、肥料及植物刺条的伤害。适用于种植、换盆、除草、修剪等各类园艺操作，是家庭园艺爱好者必备的基础工具之一。手套设计符合人体工学，佩戴舒适，操作灵活，可反复清洗使用。</t>
+          <t>虹越定制园艺通用手套，墨绿色设计，适合各类园艺操作时佩戴使用。具有良好的耐磨性和防护功能，可有效保护双手免受泥土、枝条刮伤及水渍侵扰。掌心采用防滑材质，抓握园艺工具更加稳固。透气性好，长时间佩戴舒适。适用于种植、换盆、除草、修剪等各种园艺场景，是家庭园艺爱好者的实用防护工具。</t>
         </is>
       </c>
     </row>
@@ -4228,11 +4215,9 @@
           <t>雷欧</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>雷欧6分快速接口是一种园艺灌溉系统专用的水管连接配件，采用快速卡扣设计，无需螺纹即可实现水管间的便捷连接与拆卸。规格为6分（约20mm管径），适用于家庭园艺浇水系统、滴灌设备、微喷系统等连接需求。不含内牙设计，方便与各类外牙接头或直接与水管连接。具有安装简便、密封性好、耐老化等特点，是园艺灌溉系统中常用的基础配件，可重复拆装使用，方便季节性灌溉设备的调整与维护。</t>
+          <t>雷欧6分快速接口是一款园艺灌溉系统配件，采用快速连接设计，用于3/4英寸（6分）水管系统的连接。该产品为外螺纹快速接头，不含内牙设计，安装便捷，密封性好，适用于花园灌溉、草坪浇水、蔬菜种植等多种园艺场景的水管连接与分流。材质坚固耐用，耐腐蚀，可重复使用。</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4269,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>铁线莲倒影是虹安园艺培育的藤本花卉品种，花朵大而艳丽，花色以蓝紫色系为主，花瓣质地厚实，具有较高的观赏价值。该品种攀援能力强，适合用于花架、拱门、栅栏等垂直绿化，也可作为阳台盆栽观赏。喜阳光充足、通风良好的环境，土壤宜疏松肥沃、排水良好。冬季耐寒性较强，夏季需适当遮阴。修剪方式根据品种特性而定，一般在早春进行修剪以促进新枝萌发。花期较长，可从春季延续至秋季，是花园中重要的攀援花卉之一。</t>
+          <t>铁线莲“倒影”是一款经典的藤本花卉品种，花朵通常呈淡雅色调，以白色或浅粉色为底，带有紫色或粉色的条纹或晕染，花型优美，花期较长。该品种攀援能力强，适合用于花架、拱门、篱笆、墙面等垂直绿化场景。喜阳光充足、排水良好的环境，耐寒性较好，适合全国各地大部分地区种植。倒影品种生长迅速，开花量大，是打造浪漫花园的优选品种。</t>
         </is>
       </c>
     </row>
@@ -4311,32 +4296,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>乔木</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>其他乔木</t>
+          <t>其他灌木</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>虹安果树</t>
+          <t>塔溪帝</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>柚子</t>
+          <t>香柠檬柚</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>塔溪帝</t>
+          <t>东方香柠柚（耐寒）</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>虹安果树塔溪帝东方香柠柚是一款耐寒型柚子品种，商品名为塔溪帝®。该品种具有较强的耐寒能力，适合北方地区种植。柚子果实清香、酸甜可口，富含维生素C。树形优美，可作为庭院观赏树或经济果树栽培。喜欢阳光充足的环境，适宜疏松肥沃、排水良好的土壤。耐寒品种，可在零下低温环境下露地越冬，适合庭院、阳台或果园种植。</t>
+          <t>虹安果树塔溪帝®东方香柠柚是一款耐寒型柑橘类果树苗木。该品种为东方系香柠檬柚，具有芳香浓郁、果肉鲜嫩的特点。耐寒性较强，适合北方地区种植。树形中等，生长势健壮，容易管理。果实成熟期适中，既可观赏又可食用。栽培时需选择阳光充足、排水良好的环境，土壤以微酸性至中性为宜。耐寒品种，需注意冬季防寒措施，确保安全越冬。</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4373,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>约旦枫树是槭树科槭属的落叶乔木，虹安苗圃精选培育品种。树形优美，枝叶繁茂，秋季叶片变为艳丽的橙红色或鲜红色，具有极高的观赏价值。喜光稍耐阴，适应性强，耐寒性较好，适合庭院孤植、群植或作为行道树，也可用于园林景观搭配。养护时注意保持土壤湿润，避免积水。</t>
+          <t>虹安枫树约旦品种是一款观赏性极强的彩色乔木，叶片色彩鲜艳，春季新叶呈现明亮的橙红色或黄色，夏季转为翠绿色，秋季又转为热烈的红色或橙色，具有很高的园林观赏价值。该品种树形优美，生长速度适中，适应性强，耐寒性好，适合庭院种植、园林造景或作为行道树。喜半阴环境，适宜在疏松肥沃、排水良好的土壤中生长，夏季需适当遮阴，保持土壤湿润，避免积水。</t>
         </is>
       </c>
     </row>
@@ -4428,11 +4413,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>花彩师骨粉颗粒是一种高品质有机磷肥，采用优质动物骨骼经高温灭菌、粉碎加工而成。富含磷、钙及多种微量元素，肥效持久温和，适合拌土或作基肥使用。能有效促进植物根系发育、花芽分化和果实成熟，提高抗病能力。适用于多肉植物、球根花卉、果树及各类开花植物，尤其适合补充植物所需的磷元素。无异味，不烧根，是家庭园艺的理想选择。建议与土壤混合使用，每季度施用一次即可。</t>
+          <t>花彩师骨粉颗粒是一种高品质有机肥料，以优质动物骨骼为原料，经过高温灭菌和精细加工制成。富含磷、钙等营养元素，肥效缓释持久，能有效促进植物根系生长发育，增强抗病抗逆能力。颗粒状设计便于均匀撒施和土壤混合，适合作为底肥或追肥使用。广泛应用于花卉、果树、蔬菜等各类植物，尤其对开花结果类植物效果显著，能明显提高开花质量和果实品质。使用时建议穴施或条施，每亩用量约50-100公斤，可根据土壤条件和植物需求适当调整。</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4450,11 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>未提供</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -4480,7 +4467,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>大花绣球龙宫是绣球花的一个品种，以其大而饱满的花球著称。花色丰富，通常在酸性土壤中呈现蓝色，碱性土壤中呈现粉红色。花期集中在夏季，观赏价值极高，适合庭院种植或盆栽观赏。喜半阴环境，需保持土壤湿润，避免强光直射。冬季适当修剪枯枝，有助于来年开花。</t>
+          <t>大花绣球龙宫是绣球花的一个经典品种，花朵硕大饱满，呈球形或伞房状花序，具有很高的观赏价值。该品种适应性强，耐阴性好，适合种植于庭院、花园或阳台等场所。绣球花色会随土壤酸碱度变化而呈现蓝色或粉色，养护相对简单，喜欢半阴环境，需保持土壤湿润但避免积水，冬季适当修剪枯枝有利于来年开花。</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4499,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>其他专用介质</t>
+          <t>花卉专用介质</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4520,11 +4507,9 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>成都神龙月季小盆扦插基质，容量60L，专为月季扦插繁殖设计的优质培养基质。该基质采用科学配比，具有良好的透气性、保水性和排水性，能够为扦插枝条提供适宜的生根环境，促进根系快速发育，提高扦插成活率。适用于月季小盆扦插、枝条繁殖等园艺活动，是月季爱好者进行无性繁殖的理想选择。使用时保持基质湿润，避免积水，注意遮阴防晒。</t>
+          <t>成都神龙月季小盆扦插基质，容量60L，专用花卉扦插配方介质。该基质经过科学配比，透气性佳、保水性好，适合月季等花卉的扦插繁殖使用。基质酸碱度适宜，含适量营养成分，能促进插条生根，提高扦插成活率。适用于家庭园艺中月季小盆扦插育苗，是繁殖月季的理想介质材料。使用时保持基质湿润但不积水，注意通风透气。</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4561,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>蓝莓'沃农'是虹安果树品牌的优质种苗，植株为灌木类型，株型紧凑，适合家庭园艺种植。果实呈深蓝色，果肉细腻，酸甜可口，富含花青素，营养价值高。喜酸性土壤（pH值4.5-5.5），喜阳光充足的环境，需适当修剪以促进新枝萌发，提高产量。适宜盆栽或庭院地栽，是一种兼具观赏性和食用价值的经济果树。</t>
+          <t>蓝莓是一种营养价值极高的灌木果树，果实富含花青素，具有抗氧化、保护视力等功效。"沃农"品种为蓝莓优质品种，适应性较强，果实口感酸甜可口，适合家庭园艺种植。喜酸性土壤（pH值4.5-5.5），需充足阳光和良好排水，生长季节保持土壤湿润但避免积水。植株较小巧，适合庭院盆栽或地栽，一般定植后2-3年开始结果，盛果期可达10年以上。</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4596,11 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>未提供</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -4624,7 +4613,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>冬青“先令”是冬青科冬青属的常绿乔木品种。叶色深绿，秋季结出红色浆果，挂果期长，观赏价值高。耐寒性强，适应性广，适合庭院种植或作为行道树。“方块”可能指方形修剪造型或方形容器栽培，整体株型规整美观，适合景观配置或室内观赏。喜阳光充足的环境，耐修剪，养护相对简单。</t>
+          <t>冬青“先令”是一款常绿乔木品种，株型紧凑健壮，叶片呈深绿色且有光泽，四季常青。秋季结果，浆果鲜红或黄色，观赏性极佳。常用于庭院绿化、行道树或造型苗栽培。喜阳光充足的环境，耐寒性较强，适应多种土壤类型。养护相对简单，浇水遵循见干见湿原则，定期施肥促进生长。</t>
         </is>
       </c>
     </row>
@@ -4664,11 +4653,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>花彩师绣球调蓝剂是一种专为绣球花设计的植物花朵颜色调节产品，主要成分为硫酸铝等酸性物质。通过调节土壤酸碱度（降低pH值），帮助绣球花呈现蓝色或蓝紫色花朵。三联包设计方便分次使用，45g规格适合家庭园艺使用。使用时需按照说明稀释后浇灌于植株根部，避免直接接触叶片。通常在绣球花芽分化期或花蕾形成期使用效果更佳，注意薄肥勤施，避免浓度过高造成肥害。</t>
+          <t>花彩师绣球调蓝剂是一种园艺专用肥料，主要用于调节绣球花的花色。本品为三联包设计，总净含量45g，便于分次使用和保存。调蓝剂能有效降低土壤pH值，为绣球提供充足的铝离子，促使绣球花呈现鲜艳的蓝色。使用时需按说明稀释后浇灌，注意避开高温时段。该产品特别适用于喜欢蓝色绣球的园艺爱好者，可帮助绣球花在酸性土壤条件下开出理想的花色。</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4707,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>铁线莲是经典的藤本花卉，被誉为“藤本皇后”。风之森林品种花量大，花朵呈优雅的钟形或星形，花色清新素雅，攀援能力强，适合用于花架、廊架、墙面、篱笆等垂直绿化。喜光照充足、排水良好的环境，根系喜凉爽，夏季需适当遮荫。冬季耐寒性好，地上部分枯萎后次年可重新萌发。需定期施肥和修剪，以促进开花。</t>
+          <t>铁线莲是毛茛科铁线莲属的多年生藤本植物，享有“藤本皇后”之美誉。风之森林品种花型优美，花色清新，适合攀爬于廊架、围栏、拱门等支撑物上种植。喜阳光充足、排水良好的环境，根系喜凉爽，夏季需适当遮阴。耐寒性较强，冬季地上部分枯萎后翌年可重新萌发。开花时繁花似锦，是庭院垂直绿化的优良材料。</t>
         </is>
       </c>
     </row>
@@ -4755,11 +4742,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>XQZ</t>
-        </is>
-      </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -4772,7 +4754,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>大花绣球龙宫是绣球花中的一个优质品种，花朵硕大饱满，花色艳丽夺目，具有极高的观赏价值。该品种适应性强，喜半阴环境，耐寒性较好，适合庭院种植或盆栽观赏。花期通常在夏季，盛开时如球状花序团簇成片，极具装饰效果。养护时需保持土壤湿润，避免强光直射，冬季适当修剪枯枝以促进新枝萌发。</t>
+          <t>大花绣球龙宫是一种美丽的落叶灌木植物，花朵大而饱满，呈球形或伞房状花序，花色丰富艳丽，观赏价值极高。该品种具有分枝性好、开花整齐的特点，适合庭院种植、园林景观布置或盆栽观赏。喜半阴环境，耐寒性较好，需要保持土壤湿润但排水良好，定期施肥可促进花大色艳。</t>
         </is>
       </c>
     </row>
@@ -4812,11 +4794,9 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>马雅Maya90浓缩营养液是一款通用型植物肥料，规格为10ml单支装。产品采用高浓度配方设计，稀释后适用于各类室内绿植、花卉、蔬菜等的追肥使用。浓缩型设计便于储存和使用，只需按照说明比例稀释即可。可快速补充植物生长所需的氮磷钾等营养元素，促进植物健康生长，增强植株抗病能力。使用时建议遵循薄肥勤施的原则，避免浓度过高造成肥害。</t>
+          <t>马雅Maya90浓缩营养液是一款通用型植物肥料，容量为10ml单支装。采用高浓度配方设计，富含植物生长所需的氮磷钾及微量元素，适用于各类室内外观赏植物、蔬菜、果树等的追肥使用。使用时需按照说明稀释后浇灌或叶面喷施，可快速补充植株营养，促进生长健壮、叶色浓绿、花果繁茂。浓缩型设计便于保存和定量使用，是家庭园艺常用的便捷型液体肥料。</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4848,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>虹安果树蓝莓'蓝葡萄'是一款优良的中晚熟蓝莓品种，植株生长健壮，树冠开张，适应性较强。果实呈深蓝色，果粉厚实，大小均匀，甜度高，带有独特的葡萄香气，风味佳。成熟期较晚，可延长采收期，适合家庭园艺种植和商业栽培。喜酸性土壤（pH值4.5-5.5），需充足的阳光照射，生长期间保持土壤湿润但不积水，每年冬季需进行适度修剪以促进新枝萌发，提高来年产量。</t>
+          <t>蓝莓“蓝葡萄”是一种灌木类果树苗木，植株长势中等，树形开张，适应性强。果实为深蓝色，果粉浓厚，口感甜酸适中，香气浓郁，品质优良。该品种早熟丰产，果实耐储运，适合家庭园艺种植。喜酸性土壤（pH值4.5-5.5），需阳光充足的环境，生长期需保持土壤湿润但不积水。每年春季萌芽前可适当修剪，促进新枝生长，提高结果量。</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4880,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>花卉专用介质</t>
+          <t>其他专用介质</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4908,11 +4888,9 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>花彩师蓝绣球专用型介质是专为绣球植物研发的高品质栽培介质，容量为8L。该介质针对绣球的生长习性和需酸特性进行科学配比，富含绣球生长所需的营养元素，酸碱度适宜，能够有效维持土壤酸性环境，促进绣球根系发育健壮，显著提升绣球的开花品质和色彩表现。适用于家庭园艺中绣球盆栽或地栽的换盆、改良土壤等场景。使用时可直接作为栽培基质使用，或与园土混合调配，种植后保持介质湿润即可。</t>
+          <t>花彩师蓝绣球专用型介质是专为绣球植物配制的栽培基质，容量为8升。该介质针对绣球喜酸特性优化pH值，含有适量铝元素有助于促进蓝色花色形成。介质配方通透性好、保水性强，适合绣球上盆、换盆及地栽改良使用，为绣球根系提供良好的生长环境。</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4932,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>果树</t>
+          <t>小青柠</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4964,7 +4942,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>虹安果树G花叶小青柠“奶茶”是一款观赏与食用兼顾的果树盆栽。小青柠为灌木类柑橘植物，叶片带有花叶纹样，具有较高观赏价值。成熟果实呈青绿色，酸甜可口，可鲜食或制作饮品。喜阳光充足环境，耐半阴，生长适温15-28℃，适合庭院种植或阳台盆栽。养护需保持土壤湿润但忌积水，生长期适当施肥，促进果实发育。</t>
+          <t>花叶小青柠是芸香科柑橘属的灌木或小乔木植物，'奶茶'是其一个特色品种，叶片带有斑驳的纹理，呈花叶状，观赏价值较高。该品种株型紧凑，适合盆栽或庭院种植，既能观叶观果，果实为小型青柠，成熟时呈黄色或青绿色，果肉酸香可口，可食用或做调味品。喜温暖湿润环境，耐半阴，需要充足光照以保证果实品质，较耐旱，适宜疏松排水良好的微酸性土壤。</t>
         </is>
       </c>
     </row>
@@ -5006,7 +4984,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>圆叶葡萄</t>
+          <t>葡萄</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5016,7 +4994,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>圆叶葡萄格威尔是一种多年生藤本果树，果实品质优良，适应性强。树势中庸，适宜棚架或篱架栽培，需搭设支架供其攀爬生长。喜阳光充足、排水良好的环境，栽植时需选择光照充足的位置。格威尔品种具有较强的抗病性，耐寒性较好，适合家庭园艺种植。栽植后注意合理修剪，保持良好通风透光，及时施肥浇水，可获得丰产优质的果实。适合庭院、阳台种植，既可观赏又可采收鲜食。</t>
+          <t>圆叶葡萄“格威尔”是虹安果树推出的优质葡萄品种，果粒圆形，成熟时果皮呈紫黑色，果肉多汁味甜，富含花青素和维生素。花序美观，既可食用也可作为庭院观赏藤本栽培。适应性强，耐寒耐热，适合家庭果园或阳台盆栽种植，搭架牵引后可快速覆盖棚架，夏日遮荫纳凉，秋季收获甜美果实。</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5029,11 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>未提供</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -5064,7 +5046,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>冬青"皇帝"是冬青科的常绿乔木品种，树形端正美观，枝叶繁茂。其叶片深绿有光泽，冬季挂满红色浆果，观赏价值极高。常用于庭院景观、行道树或园林绿化配置。该品种适应性较强，喜阳光充足的环境，耐寒性较好，对土壤要求不严，排水良好的土壤更利于生长。修剪管理相对简单，适合家庭园艺种植。</t>
+          <t>冬青'皇帝'是冬青科冬青属的常绿乔木品种，树形端正，生长旺盛，叶片深绿且有光泽，冬季结满鲜艳的红色浆果，挂果期长，具有极高的观赏价值。该品种耐寒性强，适应范围广，适合庭院孤植或列植，也可作为行道树使用。养护需注意保持土壤湿润偏酸，定期修剪枝条以保持良好树形。</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5083,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>安酷</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5109,10 +5091,14 @@
           <t>栀子花</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>开呀开3号</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>栀子花是茜草科栀子属的常绿灌木，原产于中国中部和南部。其叶片浓绿光亮，花朵洁白芬芳，具有浓郁的香气，深受园艺爱好者喜爱。该品种株型紧凑，适合庭院种植或盆栽观赏。栀子花喜酸性土壤和充足光照，需要保持土壤湿润但避免积水。花期在春夏季，开花时香气四溢，可用于美化庭院、阳台或作为室内观花植物。养护时需注意防寒保暖，北方地区冬季需移入室内。</t>
+          <t>栀子花是茜草科栀子属的常绿灌木植物，原产中国南方地区。其叶片浓绿光亮，花朵洁白芳香，具有很高的观赏价值。该品种为灌木类种苗，适合庭院种植或盆栽观赏。喜温暖湿润环境，喜酸性土壤，适宜生长温度为18-25℃。需保持充足光照但避免暴晒，生长期保持土壤湿润但忌积水。春季施用复合肥促进开花，花后可适当修剪整形。繁殖常用扦插和分株方式。</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5135,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>安酷</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5164,7 +5150,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>栀子花开呀开2号是栀子花的一个品种，属于茜草科栀子属灌木植物。该品种以其芳香洁白的花朵著称，花朵大而饱满，香气浓郁。喜阳光充足、温暖湿润的环境，适合种植在疏松肥沃、排水良好的酸性土壤中。花期通常在春末夏初，具有较高的观赏价值，可用于庭院种植或盆栽观赏。养护时需注意保持土壤酸性，适时施肥修剪。</t>
+          <t>栀子花是茜草科栀子属的常绿灌木，原产中国长江流域。叶片浓绿光亮，花朵洁白芳香，单瓣或重瓣，具有较高的观赏价值。喜温暖湿润、阳光充足的环境，较耐阴，适宜疏松肥沃、排水良好的酸性土壤。本品为盆栽种苗，株型紧凑，适合阳台、庭院种植，花期5-7月，香气浓郁，可用于庭院点缀或室内观赏。养护时注意保持土壤酸性，夏季适当遮阴，冬季注意防寒。</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5202,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>无刺花椒是花椒的优良品种，因枝干基本无刺而得名，便于采摘管理。该品种适应性强，耐寒耐旱，对土壤要求不严，在我国大部分地区均可种植。作为经济树种，花椒主要用于调味品生产，其果实可提取芳香油，也可作为中药材使用。成年树高约2-4米，枝叶繁茂，果实成熟时呈红色或紫红色，香气浓郁。适宜庭院种植或规模化经济栽培。</t>
+          <t>无刺花椒是花椒的优良品种，枝干无刺或刺极少，便于采摘管理。该品种适应性广，耐寒耐旱，适合庭院种植或规模栽培。果实香气浓郁，麻味纯正，是常见的食用香辛料，也可作为篱笆或防护植物栽种。喜阳光充足的环境，土壤要求不严，管理相对简单。</t>
         </is>
       </c>
     </row>
